--- a/excel/EX03_ash_sodium.xlsx
+++ b/excel/EX03_ash_sodium.xlsx
@@ -1267,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E47"/>
+  <dimension ref="B1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1567,119 +1567,137 @@
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>醬油 換算成 mg/100 g（÷ 密度 1.18）</t>
+          <t>醬油 量測 vs 標示差異 (%)</t>
         </is>
       </c>
       <c r="C34" s="14">
-        <f>'6_資料庫比對'!F21</f>
+        <f>'5_標示比較'!G5</f>
         <v/>
       </c>
       <c r="D34" s="15" t="n">
-        <v>5096.271186440678</v>
+        <v>-10.06580259222331</v>
       </c>
       <c r="E34" s="13">
-        <f>IF(ABS(C34-D34)&lt;=0.5096271196440678,"✔ 一致","✘ 不一致（換成班級數據後本來就會不同）")</f>
+        <f>IF(ABS(C34-D34)&lt;=0.0010065812592223314,"✔ 一致","✘ 不一致（換成班級數據後本來就會不同）")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="10" t="inlineStr">
         <is>
+          <t>醬油 換算成 mg/100 g（÷ 密度 1.18）</t>
+        </is>
+      </c>
+      <c r="C35" s="14">
+        <f>'6_資料庫比對'!F21</f>
+        <v/>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>5096.271186440678</v>
+      </c>
+      <c r="E35" s="13">
+        <f>IF(ABS(C35-D35)&lt;=0.5096271196440678,"✔ 一致","✘ 不一致（換成班級數據後本來就會不同）")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="10" t="inlineStr">
+        <is>
           <t>糙米灰分 資料庫合理範圍上限 (%)</t>
         </is>
       </c>
-      <c r="C35" s="11">
+      <c r="C36" s="11">
         <f>'6_資料庫比對'!J18</f>
         <v/>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D36" s="12" t="n">
         <v>1.47545</v>
       </c>
-      <c r="E35" s="13">
-        <f>IF(ABS(C35-D35)&lt;=0.000147546,"✔ 一致","✘ 不一致（換成班級數據後本來就會不同）")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="16" t="inlineStr">
+      <c r="E36" s="13">
+        <f>IF(ABS(C36-D36)&lt;=0.000147546,"✔ 一致","✘ 不一致（換成班級數據後本來就會不同）")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>「Colab 筆記本的值」是用內建模擬數據算出的答案；換成全班數據後，這一欄就不再適用。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="3" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>相關連結</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>本週實驗投影片</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>https://tai-shengyeh.github.io/food-analysis-lab/labs/w03_ash_sodium/index.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>進階：Colab 筆記本（Python）</t>
+          <t>本週實驗投影片</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>https://colab.research.google.com/github/Tai-ShengYeh/food-analysis-lab/blob/main/notebooks/NB03_ash_sodium.ipynb</t>
+          <t>https://tai-shengyeh.github.io/food-analysis-lab/labs/w03_ash_sodium/index.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="17" t="inlineStr">
         <is>
+          <t>進階：Colab 筆記本（Python）</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>https://colab.research.google.com/github/Tai-ShengYeh/food-analysis-lab/blob/main/notebooks/NB03_ash_sodium.ipynb</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="17" t="inlineStr">
+        <is>
           <t>數據分析工具指南（Excel／Orange／Colab）</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>https://tai-shengyeh.github.io/food-analysis-lab/tools.html</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+    <row r="44">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>小提醒</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>•  本檔的數據是模擬教學資料，不是真實量測值。</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="B45" s="4" t="inlineStr">
+    <row r="46" ht="45" customHeight="1">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>•  進階：資料庫比對的完整版（每一組鈉的逐一比對、每個品項的小圖、ISE／方法的說明文字、R 語言版本）與結果匯出 CSV，請看 Colab 筆記本。本檔的旗標是同一套規則的簡化版（單位 10 倍、NaCl 2.542 倍、稀釋倍數、乾濕基）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>•  灰分是濕基（除以樣品濕重）。要換成乾基：乾基灰分 = 濕基灰分 ÷ (1 − 水分%/100)，水分用 W2 的結果。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>•  灰分是濕基（除以樣品濕重）。要換成乾基：乾基灰分 = 濕基灰分 ÷ (1 − 水分%/100)，水分用 W2 的結果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>•  Google 試算表也能開這個檔（檔案 → 匯入），公式都一樣能用。看到 #NAME? 表示 Excel 版本太舊，請改用 Google 試算表。</t>
         </is>
@@ -1694,10 +1712,10 @@
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B48:E48"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B5:E5"/>
@@ -1707,9 +1725,9 @@
     <mergeCell ref="B22:E22"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -9059,7 +9077,7 @@
         <v/>
       </c>
       <c r="F5" s="31">
-        <f>'3_鈉與NaCl'!M19</f>
+        <f>'3_鈉與NaCl'!M19/'6_資料庫比對'!$H$10</f>
         <v/>
       </c>
       <c r="G5" s="39">
@@ -9072,7 +9090,7 @@
       </c>
       <c r="J5" s="16" t="inlineStr">
         <is>
-          <t>E＝C÷D×100；F 從「3_鈉與NaCl」M 欄抓；差異 %＝（量測 − 標示）÷ 標示 × 100。</t>
+          <t>E＝C÷D×100；F 從「3_鈉與NaCl」M 欄抓（醬油再除以密度）；差異 %＝（量測 − 標示）÷ 標示 × 100。</t>
         </is>
       </c>
     </row>
@@ -9146,7 +9164,7 @@
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>注意：醬油的量測值其實是 mg/100 mL，標示是 mg/100 g。這裡跟 Colab 一樣直接比（沒有除以密度）；若除以密度 1.18 g/mL，量測會變成約 5096 mg/100 g，反而比標示低約 10%。</t>
+          <t>醬油是液體，量測值是 mg/100 mL，標示是 mg/100 g，所以 F 欄先除以密度（1.18 g/mL，教學假設，在「6_資料庫比對」H10 可改）。沒除密度會算出比標示高約 6%，除了之後反而低約 10%——基準沒對齊，結論會相反。</t>
         </is>
       </c>
     </row>
@@ -35443,7 +35461,7 @@
     <row r="7" ht="32" customHeight="1">
       <c r="B7" s="52" t="inlineStr">
         <is>
-          <t>問題 2：NaCl 當量換算：某即食湯粉以去離子水稀釋 1:20 後，Na⁺ ISE 讀數為 420 ppm。求原湯粉萃取液中的 Na 濃度 (g/100 mL) 與 NaCl 當量 (g/100 mL)。</t>
+          <t>問題 2：NaCl 當量換算：某即食湯依包裝沖泡好後，以去離子水稀釋 1:20，Na⁺ ISE 讀數為 420 ppm。求沖泡好的湯中的 Na 濃度 (g/100 mL) 與 NaCl 當量 (g/100 mL)。</t>
         </is>
       </c>
     </row>
